--- a/.claude/skills/carf-peer-support-accreditation/providers/example-peer-agency/data/Evidence_and_Data_Workbook.xlsx
+++ b/.claude/skills/carf-peer-support-accreditation/providers/example-peer-agency/data/Evidence_and_Data_Workbook.xlsx
@@ -2374,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:O152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>1J-01 Technology and System Planning</t>
+          <t>1J-01 Rights of the Persons Served</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>1J-02 Information Security and Confidentiality of Data</t>
+          <t>1J-02 Grievances, Complaints, and Appeals</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="L67" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M67" s="14" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>1J-03 Social Media, Mobile Devices, and Electronic Communication</t>
+          <t>1J-03 Confidentiality and Release of Information</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr"/>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>1J-04 Information and Communication Technology in Service Delivery (Telehealth)</t>
+          <t>1J-04 Informed Consent for Services</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Technology and System Plan</t>
+          <t>COMPLETED: Your Rights — Handout for Persons Served</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr"/>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Every person served</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: System Downtime Service Log and Procedure</t>
+          <t>COMPLETED: Complaint / Grievance Form</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L71" s="14" t="inlineStr">
         <is>
-          <t>All staff</t>
+          <t>Person served, family, guardian, or any stakeholder</t>
         </is>
       </c>
       <c r="M71" s="14" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Device and System Access Log</t>
+          <t>COMPLETED: Grievance and Complaint Log</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Technology and Information Security</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr"/>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>1K-01 Rights of the Persons Served</t>
+          <t>COMPLETED: Consent for Services</t>
         </is>
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr"/>
@@ -5799,12 +5799,12 @@
       <c r="J73" s="14" t="inlineStr"/>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Person served or legal representative</t>
         </is>
       </c>
       <c r="M73" s="14" t="inlineStr"/>
@@ -5821,12 +5821,12 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>1K-02 Grievances, Complaints, and Appeals</t>
+          <t>COMPLETED: Authorization to Release Information</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr"/>
@@ -5846,12 +5846,12 @@
       <c r="J74" s="14" t="inlineStr"/>
       <c r="K74" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Person served or legal representative</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr"/>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>1K-03 Confidentiality and Release of Information</t>
+          <t>COMPLETED: Acknowledgment of Receipt — Notice of Privacy Practices</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr"/>
@@ -5893,12 +5893,12 @@
       <c r="J75" s="14" t="inlineStr"/>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="L75" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>Person served</t>
         </is>
       </c>
       <c r="M75" s="14" t="inlineStr"/>
@@ -5915,12 +5915,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>1K-04 Informed Consent for Services</t>
+          <t>COMPLETED: Annual Review — Were Rights Actually Honored?</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr"/>
@@ -5940,12 +5940,12 @@
       <c r="J76" s="14" t="inlineStr"/>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Program Director name] and [FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Your Rights — Handout for Persons Served</t>
+          <t>1K-01 Accessibility</t>
         </is>
       </c>
       <c r="C77" s="14" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L77" s="14" t="inlineStr">
         <is>
-          <t>Every person served</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="M77" s="14" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Complaint / Grievance Form</t>
+          <t>Accessibility Plan</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>Person served, family, guardian, or any stakeholder</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Grievance and Complaint Log</t>
+          <t>COMPLETED: Accessibility Barrier Survey</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L79" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer with input from persons served and personnel</t>
         </is>
       </c>
       <c r="M79" s="14" t="inlineStr"/>
@@ -6103,22 +6103,22 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Consent for Services</t>
+          <t>1L-01 Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr"/>
@@ -6128,12 +6128,12 @@
       <c r="J80" s="14" t="inlineStr"/>
       <c r="K80" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>Person served or legal representative</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr"/>
@@ -6150,22 +6150,22 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Authorization to Release Information</t>
+          <t>Performance Measurement and Management Plan</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F81" s="14" t="inlineStr"/>
@@ -6175,12 +6175,12 @@
       <c r="J81" s="14" t="inlineStr"/>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="L81" s="14" t="inlineStr">
         <is>
-          <t>Person served or legal representative</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="M81" s="14" t="inlineStr"/>
@@ -6197,17 +6197,17 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Acknowledgment of Receipt — Notice of Privacy Practices</t>
+          <t>COMPLETED: Measure Definition Sheet</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
@@ -6222,12 +6222,12 @@
       <c r="J82" s="14" t="inlineStr"/>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>Person served</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr"/>
@@ -6244,17 +6244,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Annual Review — Were Rights Actually Honored?</t>
+          <t>COMPLETED: Quarterly Performance Dashboard</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
@@ -6269,12 +6269,12 @@
       <c r="J83" s="14" t="inlineStr"/>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="L83" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name] and [FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M83" s="14" t="inlineStr"/>
@@ -6291,17 +6291,17 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>1L-01 Accessibility</t>
+          <t>1M-01 Performance Improvement</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -6316,12 +6316,12 @@
       <c r="J84" s="14" t="inlineStr"/>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr"/>
@@ -6338,17 +6338,17 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Accessibility Plan</t>
+          <t>Performance Improvement Plan and Annual Analysis Template</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
@@ -6363,7 +6363,7 @@
       <c r="J85" s="14" t="inlineStr"/>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="L85" s="14" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Accessibility Barrier Survey</t>
+          <t>COMPLETED: Annual Performance Analysis Report — Cover and Sign-Off</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Performance Measurement and Improvement</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -6410,12 +6410,12 @@
       <c r="J86" s="14" t="inlineStr"/>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer with input from persons served and personnel</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>1M-01 Performance Measurement and Management</t>
+          <t>COMPLETED: Performance Improvement Project Charter</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F87" s="14" t="inlineStr"/>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L87" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="M87" s="14" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management Plan</t>
+          <t>COMPLETED: "You Said, We Did" — Results Summary for Persons Served and Stakeholders</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr"/>
@@ -6526,22 +6526,22 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Measure Definition Sheet</t>
+          <t>2A-01 Program Description and Service Structure</t>
         </is>
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F89" s="14" t="inlineStr"/>
@@ -6551,12 +6551,12 @@
       <c r="J89" s="14" t="inlineStr"/>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M89" s="14" t="inlineStr"/>
@@ -6573,22 +6573,22 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Quarterly Performance Dashboard</t>
+          <t>2A-02 Community Resources and Coordination of Care</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr"/>
@@ -6598,12 +6598,12 @@
       <c r="J90" s="14" t="inlineStr"/>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr"/>
@@ -6620,22 +6620,22 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>1N-01 Performance Improvement</t>
+          <t>COMPLETED: Program Description</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F91" s="14" t="inlineStr"/>
@@ -6645,12 +6645,12 @@
       <c r="J91" s="14" t="inlineStr"/>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="L91" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M91" s="14" t="inlineStr"/>
@@ -6667,22 +6667,22 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Performance Improvement Plan and Annual Analysis Template</t>
+          <t>COMPLETED: Community Resource Directory</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr"/>
@@ -6692,12 +6692,12 @@
       <c r="J92" s="14" t="inlineStr"/>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr"/>
@@ -6714,17 +6714,17 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Annual Performance Analysis Report — Cover and Sign-Off</t>
+          <t>COMPLETED: Staffing Plan</t>
         </is>
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
@@ -6739,12 +6739,12 @@
       <c r="J93" s="14" t="inlineStr"/>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="L93" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M93" s="14" t="inlineStr"/>
@@ -6761,22 +6761,22 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Performance Improvement Project Charter</t>
+          <t>2B-01 Screening, Eligibility, and Access to Services</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr"/>
@@ -6786,12 +6786,12 @@
       <c r="J94" s="14" t="inlineStr"/>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr"/>
@@ -6808,22 +6808,22 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: "You Said, We Did" — Results Summary for Persons Served and Stakeholders</t>
+          <t>2B-02 Orientation of the Person Served</t>
         </is>
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>Performance Measurement and Improvement</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F95" s="14" t="inlineStr"/>
@@ -6833,12 +6833,12 @@
       <c r="J95" s="14" t="inlineStr"/>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="L95" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M95" s="14" t="inlineStr"/>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>2A-01 Program Description and Service Structure</t>
+          <t>COMPLETED: Screening and Referral Form</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr"/>
@@ -6880,12 +6880,12 @@
       <c r="J96" s="14" t="inlineStr"/>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Staff receiving the referral</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr"/>
@@ -6902,12 +6902,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>2A-02 Community Resources and Coordination of Care</t>
+          <t>COMPLETED: Waiting List Log</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F97" s="14" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       <c r="J97" s="14" t="inlineStr"/>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="L97" s="14" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Program Description</t>
+          <t>COMPLETED: Orientation of the Person Served</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
@@ -6974,12 +6974,12 @@
       <c r="J98" s="14" t="inlineStr"/>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Peer Support Specialist with the person served</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr"/>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Community Resource Directory</t>
+          <t>COMPLETED: Referral-Out Log (People We Could Not Serve)</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
@@ -7021,7 +7021,7 @@
       <c r="J99" s="14" t="inlineStr"/>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="L99" s="14" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Staffing Plan</t>
+          <t>2C-01 Person-Centered Planning</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr"/>
@@ -7068,7 +7068,7 @@
       <c r="J100" s="14" t="inlineStr"/>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>2B-01 Screening, Eligibility, and Access to Services</t>
+          <t>2C-02 Plan Review and Documentation of Services</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
@@ -7115,12 +7115,12 @@
       <c r="J101" s="14" t="inlineStr"/>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="L101" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M101" s="14" t="inlineStr"/>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>2B-02 Orientation of the Person Served</t>
+          <t>COMPLETED: Person-Centered Plan</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr"/>
@@ -7162,12 +7162,12 @@
       <c r="J102" s="14" t="inlineStr"/>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr"/>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Screening and Referral Form</t>
+          <t>COMPLETED: Person-Centered Plan Review</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
@@ -7209,12 +7209,12 @@
       <c r="J103" s="14" t="inlineStr"/>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="L103" s="14" t="inlineStr">
         <is>
-          <t>Staff receiving the referral</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M103" s="14" t="inlineStr"/>
@@ -7231,12 +7231,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Waiting List Log</t>
+          <t>COMPLETED: My Wellness and Recovery Plan</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -7256,12 +7256,12 @@
       <c r="J104" s="14" t="inlineStr"/>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served, supported by their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr"/>
@@ -7278,12 +7278,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Orientation of the Person Served</t>
+          <t>COMPLETED: Peer Support Progress Note</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
@@ -7303,12 +7303,12 @@
       <c r="J105" s="14" t="inlineStr"/>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="L105" s="14" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with the person served</t>
+          <t>The staff member who delivered the service</t>
         </is>
       </c>
       <c r="M105" s="14" t="inlineStr"/>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Referral-Out Log (People We Could Not Serve)</t>
+          <t>2D-01 Transition Planning</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr"/>
@@ -7350,7 +7350,7 @@
       <c r="J106" s="14" t="inlineStr"/>
       <c r="K106" s="14" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="L106" s="14" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>2C-01 Person-Centered Planning</t>
+          <t>2D-02 Discharge Summary and Follow-Up</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
@@ -7397,7 +7397,7 @@
       <c r="J107" s="14" t="inlineStr"/>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="L107" s="14" t="inlineStr">
@@ -7419,12 +7419,12 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>2C-02 Plan Review and Documentation of Services</t>
+          <t>COMPLETED: Transition / Discharge Summary</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr"/>
@@ -7444,12 +7444,12 @@
       <c r="J108" s="14" t="inlineStr"/>
       <c r="K108" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Peer Support Specialist and Supervisor</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr"/>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Person-Centered Plan</t>
+          <t>COMPLETED: Post-Discharge Follow-Up Contact Log</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
@@ -7491,12 +7491,12 @@
       <c r="J109" s="14" t="inlineStr"/>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="L109" s="14" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr"/>
@@ -7513,12 +7513,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Person-Centered Plan Review</t>
+          <t>COMPLETED: Unplanned Exit Review</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
@@ -7538,12 +7538,12 @@
       <c r="J110" s="14" t="inlineStr"/>
       <c r="K110" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name] with the Peer Support Specialist</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr"/>
@@ -7560,12 +7560,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: My Wellness and Recovery Plan</t>
+          <t>2E-01 Medication</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F111" s="14" t="inlineStr"/>
@@ -7585,12 +7585,12 @@
       <c r="J111" s="14" t="inlineStr"/>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="L111" s="14" t="inlineStr">
         <is>
-          <t>The person served, supported by their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M111" s="14" t="inlineStr"/>
@@ -7607,12 +7607,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Peer Support Progress Note</t>
+          <t>COMPLETED: Medication — What Your Peer Specialist Can and Cannot Do</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
@@ -7632,12 +7632,12 @@
       <c r="J112" s="14" t="inlineStr"/>
       <c r="K112" s="14" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>The staff member who delivered the service</t>
+          <t>Person served</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr"/>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>2D-01 Transition Planning</t>
+          <t>2F-01 Nonviolent Practices</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
@@ -7679,7 +7679,7 @@
       <c r="J113" s="14" t="inlineStr"/>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="L113" s="14" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>2D-02 Discharge Summary and Follow-Up</t>
+          <t>2F-02 Crisis Response and Debriefing</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
@@ -7726,12 +7726,12 @@
       <c r="J114" s="14" t="inlineStr"/>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr"/>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Transition / Discharge Summary</t>
+          <t>COMPLETED: Crisis Debriefing Form</t>
         </is>
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -7773,12 +7773,12 @@
       <c r="J115" s="14" t="inlineStr"/>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="L115" s="14" t="inlineStr">
         <is>
-          <t>Peer Support Specialist and Supervisor</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M115" s="14" t="inlineStr"/>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Post-Discharge Follow-Up Contact Log</t>
+          <t>COMPLETED: De-escalation and Nonviolent Practices Training Log</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
@@ -7820,7 +7820,7 @@
       <c r="J116" s="14" t="inlineStr"/>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="L116" s="14" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Unplanned Exit Review</t>
+          <t>COMPLETED: My Personal Safety and Crisis Plan</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
@@ -7867,12 +7867,12 @@
       <c r="J117" s="14" t="inlineStr"/>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="L117" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name] with the Peer Support Specialist</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr"/>
@@ -7889,17 +7889,17 @@
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>2E-01 Medication</t>
+          <t>2G-01 Content and Maintenance of the Record of the Person Served</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -7914,7 +7914,7 @@
       <c r="J118" s="14" t="inlineStr"/>
       <c r="K118" s="14" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="L118" s="14" t="inlineStr">
@@ -7936,22 +7936,22 @@
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Medication — What Your Peer Specialist Can and Cannot Do</t>
+          <t>2G-02 Records Retention, Access, and Destruction</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F119" s="14" t="inlineStr"/>
@@ -7961,12 +7961,12 @@
       <c r="J119" s="14" t="inlineStr"/>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="L119" s="14" t="inlineStr">
         <is>
-          <t>Person served</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="M119" s="14" t="inlineStr"/>
@@ -7983,22 +7983,22 @@
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>2F-01 Nonviolent Practices</t>
+          <t>COMPLETED: Record Content Checklist</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F120" s="14" t="inlineStr"/>
@@ -8008,12 +8008,12 @@
       <c r="J120" s="14" t="inlineStr"/>
       <c r="K120" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or Supervisor</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr"/>
@@ -8030,22 +8030,22 @@
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>2F-02 Crisis Response and Debriefing</t>
+          <t>COMPLETED: Records Retention Schedule</t>
         </is>
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F121" s="14" t="inlineStr"/>
@@ -8055,12 +8055,12 @@
       <c r="J121" s="14" t="inlineStr"/>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="L121" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr"/>
@@ -8077,22 +8077,22 @@
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Crisis Debriefing Form</t>
+          <t>2H-01 Quality Record Review</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr"/>
@@ -8102,12 +8102,12 @@
       <c r="J122" s="14" t="inlineStr"/>
       <c r="K122" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr"/>
@@ -8124,17 +8124,17 @@
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: De-escalation and Nonviolent Practices Training Log</t>
+          <t>COMPLETED: Quality Record Review Tool</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -8149,12 +8149,12 @@
       <c r="J123" s="14" t="inlineStr"/>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="L123" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or qualified designee who did not write the documentation</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr"/>
@@ -8171,17 +8171,17 @@
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: My Personal Safety and Crisis Plan</t>
+          <t>COMPLETED: Quarterly Record Review Summary Report</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Records and Quality Review</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -8196,12 +8196,12 @@
       <c r="J124" s="14" t="inlineStr"/>
       <c r="K124" s="14" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr"/>
@@ -8218,12 +8218,12 @@
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>2G-01 Content and Maintenance of the Record of the Person Served</t>
+          <t>COMPLETED: Corrective Action Tracker</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F125" s="14" t="inlineStr"/>
@@ -8243,12 +8243,12 @@
       <c r="J125" s="14" t="inlineStr"/>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="L125" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="M125" s="14" t="inlineStr"/>
@@ -8265,17 +8265,17 @@
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>2G-02 Records Retention, Access, and Destruction</t>
+          <t>2I-01 Information and Communication Technology in Service Delivery (Telehealth)</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery Using Information and Communication Technologies</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr">
@@ -8290,12 +8290,12 @@
       <c r="J126" s="14" t="inlineStr"/>
       <c r="K126" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr"/>
@@ -8312,22 +8312,22 @@
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Record Content Checklist</t>
+          <t>3C-01 Community Integration Program Philosophy and Scope</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F127" s="14" t="inlineStr"/>
@@ -8337,12 +8337,12 @@
       <c r="J127" s="14" t="inlineStr"/>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L127" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator] or Supervisor</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr"/>
@@ -8359,22 +8359,22 @@
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Records Retention Schedule</t>
+          <t>3C-02 Choice, Self-Determination, and Dignity of Risk</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F128" s="14" t="inlineStr"/>
@@ -8384,12 +8384,12 @@
       <c r="J128" s="14" t="inlineStr"/>
       <c r="K128" s="14" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr"/>
@@ -8406,17 +8406,17 @@
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>2H-01 Quality Record Review</t>
+          <t>3C-03 Natural Supports and Community Connection</t>
         </is>
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
@@ -8431,12 +8431,12 @@
       <c r="J129" s="14" t="inlineStr"/>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L129" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M129" s="14" t="inlineStr"/>
@@ -8453,22 +8453,22 @@
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Quality Record Review Tool</t>
+          <t>3C-04 Transportation and Community Outings</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F130" s="14" t="inlineStr"/>
@@ -8478,12 +8478,12 @@
       <c r="J130" s="14" t="inlineStr"/>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator] or qualified designee who did not write the documentation</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr"/>
@@ -8500,22 +8500,22 @@
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Quarterly Record Review Summary Report</t>
+          <t>3C-05 Advocacy, Benefits, and Removing Barriers</t>
         </is>
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F131" s="14" t="inlineStr"/>
@@ -8525,12 +8525,12 @@
       <c r="J131" s="14" t="inlineStr"/>
       <c r="K131" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L131" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr"/>
@@ -8547,17 +8547,17 @@
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Corrective Action Tracker</t>
+          <t>COMPLETED: Community Integration Goal Worksheet</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Records and Quality Review</t>
+          <t>Service Delivery</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
@@ -8572,12 +8572,12 @@
       <c r="J132" s="14" t="inlineStr"/>
       <c r="K132" s="14" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr"/>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B133" s="14" t="inlineStr">
         <is>
-          <t>3CI-01 Community Integration Program Philosophy and Scope</t>
+          <t>COMPLETED: Natural Supports Map</t>
         </is>
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F133" s="14" t="inlineStr"/>
@@ -8619,12 +8619,12 @@
       <c r="J133" s="14" t="inlineStr"/>
       <c r="K133" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L133" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr"/>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>3CI-02 Choice, Self-Determination, and Dignity of Risk</t>
+          <t>COMPLETED: Community Resource Directory</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F134" s="14" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       <c r="J134" s="14" t="inlineStr"/>
       <c r="K134" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L134" s="14" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="B135" s="14" t="inlineStr">
         <is>
-          <t>3CI-03 Natural Supports and Community Connection</t>
+          <t>COMPLETED: Benefits and Entitlements Checklist</t>
         </is>
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F135" s="14" t="inlineStr"/>
@@ -8713,12 +8713,12 @@
       <c r="J135" s="14" t="inlineStr"/>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="L135" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr"/>
@@ -8735,17 +8735,17 @@
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>3CI-04 Transportation and Community Outings</t>
+          <t>3P-01 The Peer Support Service Model</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Peer Workforce</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
@@ -8760,7 +8760,7 @@
       <c r="J136" s="14" t="inlineStr"/>
       <c r="K136" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="L136" s="14" t="inlineStr">
@@ -8782,17 +8782,17 @@
       </c>
       <c r="B137" s="14" t="inlineStr">
         <is>
-          <t>3CI-05 Advocacy, Benefits, and Removing Barriers</t>
+          <t>3P-02 Self-Disclosure</t>
         </is>
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Peer Workforce</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
@@ -8807,12 +8807,12 @@
       <c r="J137" s="14" t="inlineStr"/>
       <c r="K137" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="L137" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M137" s="14" t="inlineStr"/>
@@ -8829,22 +8829,22 @@
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Community Integration Goal Worksheet</t>
+          <t>3P-03 Boundaries and Dual Relationships</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Peer Workforce</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F138" s="14" t="inlineStr"/>
@@ -8854,12 +8854,12 @@
       <c r="J138" s="14" t="inlineStr"/>
       <c r="K138" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M138" s="14" t="inlineStr"/>
@@ -8876,22 +8876,22 @@
       </c>
       <c r="B139" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Natural Supports Map</t>
+          <t>3P-04 Peer Workforce Wellness</t>
         </is>
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Peer Workforce</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F139" s="14" t="inlineStr"/>
@@ -8901,12 +8901,12 @@
       <c r="J139" s="14" t="inlineStr"/>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="L139" s="14" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="M139" s="14" t="inlineStr"/>
@@ -8923,22 +8923,22 @@
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Community Resource Directory</t>
+          <t>3P-05 Peer Specialist Credential, Scope, and Career Ladder</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Peer Workforce</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F140" s="14" t="inlineStr"/>
@@ -8948,12 +8948,12 @@
       <c r="J140" s="14" t="inlineStr"/>
       <c r="K140" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="M140" s="14" t="inlineStr"/>
@@ -8970,17 +8970,17 @@
       </c>
       <c r="B141" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Benefits and Entitlements Checklist</t>
+          <t>COMPLETED: Job Description — Peer Support Specialist</t>
         </is>
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
         <is>
-          <t>Service Delivery</t>
+          <t>Peer Workforce</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
@@ -8995,12 +8995,12 @@
       <c r="J141" s="14" t="inlineStr"/>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="L141" s="14" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>Employee and supervisor sign at hire and at revision</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr"/>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>3P-01 The Peer Support Service Model</t>
+          <t>COMPLETED: Competency Assessment — Peer Support Specialist</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F142" s="14" t="inlineStr"/>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M142" s="14" t="inlineStr"/>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="B143" s="14" t="inlineStr">
         <is>
-          <t>3P-02 Self-Disclosure</t>
+          <t>COMPLETED: Self-Disclosure Supervision Worksheet</t>
         </is>
       </c>
       <c r="C143" s="14" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F143" s="14" t="inlineStr"/>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="L143" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>3P-03 Boundaries and Dual Relationships</t>
+          <t>COMPLETED: Dual Relationship Disclosure and Management Plan</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F144" s="14" t="inlineStr"/>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Any staff member; management plan by [FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M144" s="14" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="B145" s="14" t="inlineStr">
         <is>
-          <t>3P-04 Peer Workforce Wellness</t>
+          <t>COMPLETED: My Peer Wellness Plan (Staff)</t>
         </is>
       </c>
       <c r="C145" s="14" t="inlineStr">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Completed evidence</t>
         </is>
       </c>
       <c r="F145" s="14" t="inlineStr"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="L145" s="14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr"/>
@@ -9205,17 +9205,17 @@
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>3P-05 Peer Specialist Credential, Scope, and Career Ladder</t>
+          <t>TECH-01 Technology and System Planning</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>Peer Workforce</t>
+          <t>Technology and Information Security</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
@@ -9230,7 +9230,7 @@
       <c r="J146" s="14" t="inlineStr"/>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
@@ -9252,22 +9252,22 @@
       </c>
       <c r="B147" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Job Description — Peer Support Specialist</t>
+          <t>TECH-02 Information Security and Confidentiality of Data</t>
         </is>
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
         <is>
-          <t>Peer Workforce</t>
+          <t>Technology and Information Security</t>
         </is>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F147" s="14" t="inlineStr"/>
@@ -9277,12 +9277,12 @@
       <c r="J147" s="14" t="inlineStr"/>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="L147" s="14" t="inlineStr">
         <is>
-          <t>Employee and supervisor sign at hire and at revision</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="M147" s="14" t="inlineStr"/>
@@ -9299,22 +9299,22 @@
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Competency Assessment — Peer Support Specialist</t>
+          <t>TECH-03 Social Media, Mobile Devices, and Electronic Communication</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>Peer Workforce</t>
+          <t>Technology and Information Security</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F148" s="14" t="inlineStr"/>
@@ -9324,12 +9324,12 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="L148" s="14" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M148" s="14" t="inlineStr"/>
@@ -9346,22 +9346,22 @@
       </c>
       <c r="B149" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Self-Disclosure Supervision Worksheet</t>
+          <t>2I-01 Information and Communication Technology in Service Delivery (Telehealth)</t>
         </is>
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
         <is>
-          <t>Peer Workforce</t>
+          <t>Technology and Information Security</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F149" s="14" t="inlineStr"/>
@@ -9371,12 +9371,12 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="L149" s="14" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="M149" s="14" t="inlineStr"/>
@@ -9393,22 +9393,22 @@
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: Dual Relationship Disclosure and Management Plan</t>
+          <t>Technology and System Plan</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Peer Workforce</t>
+          <t>Technology and Information Security</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>Completed evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F150" s="14" t="inlineStr"/>
@@ -9418,12 +9418,12 @@
       <c r="J150" s="14" t="inlineStr"/>
       <c r="K150" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>Any staff member; management plan by [FILL IN: Supervisor of the peer workforce]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="M150" s="14" t="inlineStr"/>
@@ -9440,17 +9440,17 @@
       </c>
       <c r="B151" s="14" t="inlineStr">
         <is>
-          <t>COMPLETED: My Peer Wellness Plan (Staff)</t>
+          <t>COMPLETED: System Downtime Service Log and Procedure</t>
         </is>
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
         <is>
-          <t>Peer Workforce</t>
+          <t>Technology and Information Security</t>
         </is>
       </c>
       <c r="E151" s="14" t="inlineStr">
@@ -9465,17 +9465,64 @@
       <c r="J151" s="14" t="inlineStr"/>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="L151" s="14" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+          <t>All staff</t>
         </is>
       </c>
       <c r="M151" s="14" t="inlineStr"/>
       <c r="N151" s="14" t="inlineStr"/>
       <c r="O151" s="14" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED: Device and System Access Log</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>X.TECH</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>Technology and Information Security</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>Completed evidence</t>
+        </is>
+      </c>
+      <c r="F152" s="14" t="inlineStr"/>
+      <c r="G152" s="14" t="inlineStr"/>
+      <c r="H152" s="14" t="inlineStr"/>
+      <c r="I152" s="14" t="inlineStr"/>
+      <c r="J152" s="14" t="inlineStr"/>
+      <c r="K152" s="14" t="inlineStr">
+        <is>
+          <t>X.TECH</t>
+        </is>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>[FILL IN: Privacy Officer]</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr"/>
+      <c r="N152" s="14" t="inlineStr"/>
+      <c r="O152" s="14" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
@@ -9487,7 +9534,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F3:F152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10054,7 +10101,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -10542,7 +10589,7 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -11610,7 +11657,7 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -11658,7 +11705,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -11994,7 +12041,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -12042,7 +12089,7 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -12090,7 +12137,7 @@
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -12730,7 +12777,7 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -13070,7 +13117,7 @@
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -13558,7 +13605,7 @@
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -14626,7 +14673,7 @@
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -14674,7 +14721,7 @@
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F107" s="14" t="inlineStr">
@@ -15010,7 +15057,7 @@
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -15058,7 +15105,7 @@
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
@@ -15106,7 +15153,7 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
@@ -15794,7 +15841,7 @@
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F130" s="14" t="inlineStr">
@@ -16134,7 +16181,7 @@
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F137" s="14" t="inlineStr">
@@ -16818,7 +16865,7 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F151" s="14" t="inlineStr">
@@ -17886,7 +17933,7 @@
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F173" s="14" t="inlineStr">
@@ -17934,7 +17981,7 @@
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F174" s="14" t="inlineStr">
@@ -18270,7 +18317,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F181" s="14" t="inlineStr">
@@ -18318,7 +18365,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F182" s="14" t="inlineStr">
@@ -18366,7 +18413,7 @@
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F183" s="14" t="inlineStr">
@@ -19102,7 +19149,7 @@
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F198" s="14" t="inlineStr">
@@ -19442,7 +19489,7 @@
       </c>
       <c r="E205" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F205" s="14" t="inlineStr">
@@ -19930,7 +19977,7 @@
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F215" s="14" t="inlineStr">
@@ -20126,7 +20173,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -20174,7 +20221,7 @@
       </c>
       <c r="E220" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="F220" s="14" t="inlineStr">
@@ -22218,7 +22265,7 @@
       </c>
       <c r="E262" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F262" s="14" t="inlineStr">
@@ -22266,7 +22313,7 @@
       </c>
       <c r="E263" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F263" s="14" t="inlineStr">
@@ -22314,7 +22361,7 @@
       </c>
       <c r="E264" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F264" s="14" t="inlineStr">
@@ -22362,7 +22409,7 @@
       </c>
       <c r="E265" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F265" s="14" t="inlineStr">
@@ -22414,7 +22461,7 @@
       </c>
       <c r="E266" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F266" s="14" t="inlineStr">
@@ -22462,7 +22509,7 @@
       </c>
       <c r="E267" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F267" s="14" t="inlineStr">
@@ -22510,7 +22557,7 @@
       </c>
       <c r="E268" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F268" s="14" t="inlineStr">
@@ -22558,7 +22605,7 @@
       </c>
       <c r="E269" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F269" s="14" t="inlineStr">
@@ -23038,7 +23085,7 @@
       </c>
       <c r="E279" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F279" s="14" t="inlineStr">
@@ -23086,7 +23133,7 @@
       </c>
       <c r="E280" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F280" s="14" t="inlineStr">
@@ -23134,7 +23181,7 @@
       </c>
       <c r="E281" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F281" s="14" t="inlineStr">
@@ -23182,7 +23229,7 @@
       </c>
       <c r="E282" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F282" s="14" t="inlineStr">
@@ -25334,7 +25381,7 @@
       </c>
       <c r="E325" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="F325" s="14" t="inlineStr">
@@ -25382,7 +25429,7 @@
       </c>
       <c r="E326" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="F326" s="14" t="inlineStr">
@@ -25430,7 +25477,7 @@
       </c>
       <c r="E327" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F327" s="14" t="inlineStr">
@@ -25478,7 +25525,7 @@
       </c>
       <c r="E328" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F328" s="14" t="inlineStr">
@@ -25530,7 +25577,7 @@
       </c>
       <c r="E329" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F329" s="14" t="inlineStr">
@@ -25578,7 +25625,7 @@
       </c>
       <c r="E330" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F330" s="14" t="inlineStr">
@@ -25626,7 +25673,7 @@
       </c>
       <c r="E331" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F331" s="14" t="inlineStr">
@@ -25674,7 +25721,7 @@
       </c>
       <c r="E332" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F332" s="14" t="inlineStr">
@@ -26014,7 +26061,7 @@
       </c>
       <c r="E339" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F339" s="14" t="inlineStr">
@@ -26502,7 +26549,7 @@
       </c>
       <c r="E349" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F349" s="14" t="inlineStr">
@@ -27570,7 +27617,7 @@
       </c>
       <c r="E371" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F371" s="14" t="inlineStr">
@@ -27618,7 +27665,7 @@
       </c>
       <c r="E372" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F372" s="14" t="inlineStr">
@@ -27954,7 +28001,7 @@
       </c>
       <c r="E379" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F379" s="14" t="inlineStr">
@@ -28002,7 +28049,7 @@
       </c>
       <c r="E380" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F380" s="14" t="inlineStr">
@@ -28050,7 +28097,7 @@
       </c>
       <c r="E381" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F381" s="14" t="inlineStr">
@@ -28690,7 +28737,7 @@
       </c>
       <c r="E394" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F394" s="14" t="inlineStr">
@@ -29030,7 +29077,7 @@
       </c>
       <c r="E401" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F401" s="14" t="inlineStr">
@@ -29518,7 +29565,7 @@
       </c>
       <c r="E411" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F411" s="14" t="inlineStr">
@@ -30586,7 +30633,7 @@
       </c>
       <c r="E433" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F433" s="14" t="inlineStr">
@@ -30634,7 +30681,7 @@
       </c>
       <c r="E434" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F434" s="14" t="inlineStr">
@@ -30970,7 +31017,7 @@
       </c>
       <c r="E441" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F441" s="14" t="inlineStr">
@@ -31018,7 +31065,7 @@
       </c>
       <c r="E442" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F442" s="14" t="inlineStr">
@@ -31066,7 +31113,7 @@
       </c>
       <c r="E443" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F443" s="14" t="inlineStr">
@@ -31754,7 +31801,7 @@
       </c>
       <c r="E457" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F457" s="14" t="inlineStr">
@@ -32094,7 +32141,7 @@
       </c>
       <c r="E464" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F464" s="14" t="inlineStr">
@@ -32870,7 +32917,7 @@
       </c>
       <c r="E480" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F480" s="14" t="inlineStr">
@@ -33158,7 +33205,7 @@
       </c>
       <c r="E486" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F486" s="14" t="inlineStr">
@@ -33206,7 +33253,7 @@
       </c>
       <c r="E487" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F487" s="14" t="inlineStr">
@@ -33254,7 +33301,7 @@
       </c>
       <c r="E488" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F488" s="14" t="inlineStr">
@@ -33794,7 +33841,7 @@
       </c>
       <c r="E499" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F499" s="14" t="inlineStr">
@@ -33842,7 +33889,7 @@
       </c>
       <c r="E500" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="F500" s="14" t="inlineStr">
@@ -33890,7 +33937,7 @@
       </c>
       <c r="E501" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="F501" s="14" t="inlineStr">
@@ -35062,7 +35109,7 @@
       </c>
       <c r="E525" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F525" s="14" t="inlineStr">
@@ -35110,7 +35157,7 @@
       </c>
       <c r="E526" s="14" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="F526" s="14" t="inlineStr">
@@ -35158,7 +35205,7 @@
       </c>
       <c r="E527" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F527" s="14" t="inlineStr">
@@ -35210,7 +35257,7 @@
       </c>
       <c r="E528" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F528" s="14" t="inlineStr">
@@ -35258,7 +35305,7 @@
       </c>
       <c r="E529" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F529" s="14" t="inlineStr">
@@ -35306,7 +35353,7 @@
       </c>
       <c r="E530" s="14" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="F530" s="14" t="inlineStr">
@@ -35498,7 +35545,7 @@
       </c>
       <c r="E534" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F534" s="14" t="inlineStr">
@@ -37006,7 +37053,7 @@
       </c>
       <c r="E564" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="F564" s="14" t="inlineStr">
@@ -37054,7 +37101,7 @@
       </c>
       <c r="E565" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="F565" s="14" t="inlineStr">
@@ -37102,7 +37149,7 @@
       </c>
       <c r="E566" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F566" s="14" t="inlineStr">
@@ -37150,7 +37197,7 @@
       </c>
       <c r="E567" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F567" s="14" t="inlineStr">
@@ -37202,7 +37249,7 @@
       </c>
       <c r="E568" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F568" s="14" t="inlineStr">
@@ -37250,7 +37297,7 @@
       </c>
       <c r="E569" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F569" s="14" t="inlineStr">
@@ -37298,7 +37345,7 @@
       </c>
       <c r="E570" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F570" s="14" t="inlineStr">
@@ -37342,7 +37389,7 @@
       </c>
       <c r="E571" s="14" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="F571" s="14" t="inlineStr">
@@ -37610,7 +37657,7 @@
       </c>
       <c r="E577" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F577" s="14" t="inlineStr">
@@ -37786,7 +37833,7 @@
       </c>
       <c r="E581" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F581" s="14" t="inlineStr">
@@ -37830,7 +37877,7 @@
       </c>
       <c r="E582" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F582" s="14" t="inlineStr">
@@ -37874,7 +37921,7 @@
       </c>
       <c r="E583" s="14" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="F583" s="14" t="inlineStr">
@@ -38270,7 +38317,7 @@
       </c>
       <c r="E592" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="F592" s="14" t="inlineStr">
@@ -38314,7 +38361,7 @@
       </c>
       <c r="E593" s="14" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="F593" s="14" t="inlineStr">
@@ -38358,7 +38405,7 @@
       </c>
       <c r="E594" s="14" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="F594" s="14" t="inlineStr">
